--- a/data/SI/SI_5_results.xlsx
+++ b/data/SI/SI_5_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/SI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="11_9E085252E48779FD7E0676B8CE278A0B5354D447" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AF3FF7E-D94D-4188-9629-89916D08C799}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_9E085252E48779FD7E0676B8CE278A0B5354D447" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC122C1C-DE31-4667-BA1D-0C82347FC0ED}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="15" r:id="rId1"/>
@@ -29,6 +29,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">EQ_damages_regioinvent!$A$1:$W$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">HH_damages_regioinvent!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">MP_results!$A$1:$H$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -994,6 +995,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1094,7 +1096,7 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1407,13 +1409,13 @@
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="138.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="138.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>238</v>
       </c>
@@ -1421,7 +1423,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>240</v>
       </c>
@@ -1429,7 +1431,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="66.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="64" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>242</v>
       </c>
@@ -1437,7 +1439,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>244</v>
       </c>
@@ -1445,7 +1447,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>246</v>
       </c>
@@ -1453,7 +1455,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>248</v>
       </c>
@@ -1461,7 +1463,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>249</v>
       </c>
@@ -1477,9 +1479,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1517,7 +1519,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -1552,7 +1554,7 @@
         <v>63500</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1587,7 +1589,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1622,7 +1624,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1657,7 +1659,7 @@
         <v>93533.694346666671</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1692,7 +1694,7 @@
         <v>45578.436133333344</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -1730,7 +1732,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1765,7 +1767,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -1803,7 +1805,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1838,7 +1840,7 @@
         <v>71667.536000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -1876,7 +1878,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1911,7 +1913,7 @@
         <v>3.5165997959183581</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1946,7 +1948,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -1981,7 +1983,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -2016,7 +2018,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -2051,7 +2053,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -2086,7 +2088,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -2121,7 +2123,7 @@
         <v>29.039084533163258</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -2156,7 +2158,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -2191,7 +2193,7 @@
         <v>1.220177609693877</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2226,7 +2228,7 @@
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -2261,7 +2263,7 @@
         <v>2.7760508515306119</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2296,7 +2298,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -2334,7 +2336,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2369,7 +2371,7 @@
         <v>4.1704080612244896</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -2407,7 +2409,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -2442,7 +2444,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -2477,7 +2479,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -2512,7 +2514,7 @@
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2547,7 +2549,7 @@
         <v>1.2300799484693881</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>95</v>
       </c>
@@ -2585,7 +2587,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -2620,7 +2622,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -2655,7 +2657,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -2690,7 +2692,7 @@
         <v>363125</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -2725,7 +2727,7 @@
         <v>49375</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -2760,7 +2762,7 @@
         <v>84375</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -2795,7 +2797,7 @@
         <v>151450</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2830,7 +2832,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -2865,7 +2867,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -2900,7 +2902,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -2938,7 +2940,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -2976,7 +2978,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -3011,7 +3013,7 @@
         <v>7204.1082352941175</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -3054,9 +3056,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -3094,7 +3096,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -3129,7 +3131,7 @@
         <v>63500</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -3164,7 +3166,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -3199,7 +3201,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -3234,7 +3236,7 @@
         <v>93533.694346666671</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -3269,7 +3271,7 @@
         <v>45578.436133333344</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -3307,7 +3309,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -3342,7 +3344,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -3380,7 +3382,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -3415,7 +3417,7 @@
         <v>71667.536000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -3453,7 +3455,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -3488,7 +3490,7 @@
         <v>3.5165997959183581</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -3523,7 +3525,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -3558,7 +3560,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -3593,7 +3595,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -3628,7 +3630,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -3663,7 +3665,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -3698,7 +3700,7 @@
         <v>29.039084533163258</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -3733,7 +3735,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -3768,7 +3770,7 @@
         <v>1.220177609693877</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -3803,7 +3805,7 @@
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -3838,7 +3840,7 @@
         <v>2.7760508515306119</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -3873,7 +3875,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -3911,7 +3913,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -3946,7 +3948,7 @@
         <v>4.1704080612244896</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -3984,7 +3986,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -4019,7 +4021,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -4054,7 +4056,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -4089,7 +4091,7 @@
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -4124,7 +4126,7 @@
         <v>1.2300799484693881</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>95</v>
       </c>
@@ -4162,7 +4164,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -4197,7 +4199,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -4232,7 +4234,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -4267,7 +4269,7 @@
         <v>363125</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -4302,7 +4304,7 @@
         <v>49375</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -4337,7 +4339,7 @@
         <v>84375</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -4372,7 +4374,7 @@
         <v>151450</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -4407,7 +4409,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -4442,7 +4444,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -4477,7 +4479,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -4515,7 +4517,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -4553,7 +4555,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -4588,7 +4590,7 @@
         <v>7204.1082352941175</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -4631,9 +4633,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4671,7 +4673,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -4706,7 +4708,7 @@
         <v>63500</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -4741,7 +4743,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -4776,7 +4778,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -4811,7 +4813,7 @@
         <v>93533.694346666671</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -4846,7 +4848,7 @@
         <v>45578.436133333344</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -4884,7 +4886,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -4919,7 +4921,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -4957,7 +4959,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -4992,7 +4994,7 @@
         <v>71667.536000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -5030,7 +5032,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -5065,7 +5067,7 @@
         <v>3.5165997959183581</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -5100,7 +5102,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -5135,7 +5137,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -5170,7 +5172,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -5205,7 +5207,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -5240,7 +5242,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -5275,7 +5277,7 @@
         <v>29.039084533163258</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -5310,7 +5312,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -5345,7 +5347,7 @@
         <v>1.220177609693877</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -5380,7 +5382,7 @@
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -5415,7 +5417,7 @@
         <v>2.7760508515306119</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -5450,7 +5452,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -5488,7 +5490,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -5523,7 +5525,7 @@
         <v>4.1704080612244896</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -5561,7 +5563,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -5596,7 +5598,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -5631,7 +5633,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -5666,7 +5668,7 @@
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -5701,7 +5703,7 @@
         <v>1.2300799484693881</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>95</v>
       </c>
@@ -5739,7 +5741,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -5774,7 +5776,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -5809,7 +5811,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -5844,7 +5846,7 @@
         <v>363125</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -5879,7 +5881,7 @@
         <v>49375</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -5914,7 +5916,7 @@
         <v>84375</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -5949,7 +5951,7 @@
         <v>151450</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -5984,7 +5986,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -6019,7 +6021,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -6054,7 +6056,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -6092,7 +6094,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -6130,7 +6132,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -6165,7 +6167,7 @@
         <v>7204.1082352941175</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -6208,19 +6210,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208BFACB-D559-4F86-A663-15A3034E80B0}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
@@ -6249,7 +6251,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>261</v>
       </c>
@@ -6285,7 +6287,7 @@
         <v>5.4792707385125787</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>263</v>
       </c>
@@ -6321,7 +6323,7 @@
         <v>6.321518830223015</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>264</v>
       </c>
@@ -6357,7 +6359,7 @@
         <v>4.7337957076028339</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>261</v>
       </c>
@@ -6393,7 +6395,7 @@
         <v>11.644676054014001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>263</v>
       </c>
@@ -6429,7 +6431,7 @@
         <v>12.701040677015801</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>264</v>
       </c>
@@ -6473,32 +6475,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.26953125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.81640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -6563,7 +6565,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -6625,11 +6627,11 @@
         <v>3.8015765302115463E-5</v>
       </c>
       <c r="U2">
-        <f>SUM(D2:T2)</f>
+        <f t="shared" ref="U2:U33" si="0">SUM(D2:T2)</f>
         <v>1.6555813785560645</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -6691,11 +6693,11 @@
         <v>7.4865209383395586E-5</v>
       </c>
       <c r="U3">
-        <f>SUM(D3:T3)</f>
+        <f t="shared" si="0"/>
         <v>11.414936361261768</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -6757,11 +6759,11 @@
         <v>9.9962619557588937E-5</v>
       </c>
       <c r="U4">
-        <f>SUM(D4:T4)</f>
+        <f t="shared" si="0"/>
         <v>1.9343393987034456</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -6823,11 +6825,11 @@
         <v>1.4500186100550001E-4</v>
       </c>
       <c r="U5">
-        <f>SUM(D5:T5)</f>
+        <f t="shared" si="0"/>
         <v>11.728090837034701</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -6889,11 +6891,11 @@
         <v>4.7073443282316589E-5</v>
       </c>
       <c r="U6">
-        <f>SUM(D6:T6)</f>
+        <f t="shared" si="0"/>
         <v>4.7142681830888291</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -6955,11 +6957,11 @@
         <v>7.0489085691464323E-5</v>
       </c>
       <c r="U7">
-        <f>SUM(D7:T7)</f>
+        <f t="shared" si="0"/>
         <v>2.8888057007139274</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -7021,11 +7023,11 @@
         <v>2.3364923246233921E-5</v>
       </c>
       <c r="U8">
-        <f>SUM(D8:T8)</f>
+        <f t="shared" si="0"/>
         <v>2.562538514495484</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -7087,11 +7089,11 @@
         <v>6.2938009708158444E-5</v>
       </c>
       <c r="U9">
-        <f>SUM(D9:T9)</f>
+        <f t="shared" si="0"/>
         <v>5.6731793609568406</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -7153,11 +7155,11 @@
         <v>5.3789354749086128E-5</v>
       </c>
       <c r="U10">
-        <f>SUM(D10:T10)</f>
+        <f t="shared" si="0"/>
         <v>6.097573165254631</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -7219,11 +7221,11 @@
         <v>1.5680800000170001E-4</v>
       </c>
       <c r="U11">
-        <f>SUM(D11:T11)</f>
+        <f t="shared" si="0"/>
         <v>2.2896578012577438</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -7285,11 +7287,11 @@
         <v>4.6207289012643939E-6</v>
       </c>
       <c r="U12">
-        <f>SUM(D12:T12)</f>
+        <f t="shared" si="0"/>
         <v>0.96457407294308672</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -7351,11 +7353,11 @@
         <v>3.957062713422714E-5</v>
       </c>
       <c r="U13">
-        <f>SUM(D13:T13)</f>
+        <f t="shared" si="0"/>
         <v>1.798037365428159</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -7417,11 +7419,11 @@
         <v>1.812163761978711E-5</v>
       </c>
       <c r="U14">
-        <f>SUM(D14:T14)</f>
+        <f t="shared" si="0"/>
         <v>1.0505541370088523</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -7483,11 +7485,11 @@
         <v>1.1660301162310001E-4</v>
       </c>
       <c r="U15">
-        <f>SUM(D15:T15)</f>
+        <f t="shared" si="0"/>
         <v>1.6441001527238674</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -7549,11 +7551,11 @@
         <v>0.1057765680983542</v>
       </c>
       <c r="U16">
-        <f>SUM(D16:T16)</f>
+        <f t="shared" si="0"/>
         <v>4606.5550843609835</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -7615,11 +7617,11 @@
         <v>0.27813995123400082</v>
       </c>
       <c r="U17">
-        <f>SUM(D17:T17)</f>
+        <f t="shared" si="0"/>
         <v>5382.1824663003326</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -7681,11 +7683,11 @@
         <v>0.59259583060398291</v>
       </c>
       <c r="U18">
-        <f>SUM(D18:T18)</f>
+        <f t="shared" si="0"/>
         <v>34164.374008079365</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -7747,11 +7749,11 @@
         <v>0.41181215276803329</v>
       </c>
       <c r="U19">
-        <f>SUM(D19:T19)</f>
+        <f t="shared" si="0"/>
         <v>22058.145416191226</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -7813,11 +7815,11 @@
         <v>0.53247499401916898</v>
       </c>
       <c r="U20">
-        <f>SUM(D20:T20)</f>
+        <f t="shared" si="0"/>
         <v>31718.671600503942</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -7879,11 +7881,11 @@
         <v>3.036898008241971</v>
       </c>
       <c r="U21">
-        <f>SUM(D21:T21)</f>
+        <f t="shared" si="0"/>
         <v>67619.839684905266</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -7945,11 +7947,11 @@
         <v>0.95747760506781876</v>
       </c>
       <c r="U22">
-        <f>SUM(D22:T22)</f>
+        <f t="shared" si="0"/>
         <v>46182.370653465681</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -8011,11 +8013,11 @@
         <v>0.47402225014155408</v>
       </c>
       <c r="U23">
-        <f>SUM(D23:T23)</f>
+        <f t="shared" si="0"/>
         <v>35032.69957227313</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -8077,11 +8079,11 @@
         <v>0.71889331997316075</v>
       </c>
       <c r="U24">
-        <f>SUM(D24:T24)</f>
+        <f t="shared" si="0"/>
         <v>24152.607166691007</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -8143,11 +8145,11 @@
         <v>1.6022675084428</v>
       </c>
       <c r="U25">
-        <f>SUM(D25:T25)</f>
+        <f t="shared" si="0"/>
         <v>39558.841950416921</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -8209,11 +8211,11 @@
         <v>0.55311587079094726</v>
       </c>
       <c r="U26">
-        <f>SUM(D26:T26)</f>
+        <f t="shared" si="0"/>
         <v>31841.930998513359</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -8275,11 +8277,11 @@
         <v>1.1295796034574559</v>
       </c>
       <c r="U27">
-        <f>SUM(D27:T27)</f>
+        <f t="shared" si="0"/>
         <v>52887.623322852844</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -8341,11 +8343,11 @@
         <v>0.62244306262966587</v>
       </c>
       <c r="U28">
-        <f>SUM(D28:T28)</f>
+        <f t="shared" si="0"/>
         <v>15037.074875070521</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -8407,11 +8409,11 @@
         <v>0.33349284174783711</v>
       </c>
       <c r="U29">
-        <f>SUM(D29:T29)</f>
+        <f t="shared" si="0"/>
         <v>12464.226112936094</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -8473,11 +8475,11 @@
         <v>1.1770402884537361</v>
       </c>
       <c r="U30">
-        <f>SUM(D30:T30)</f>
+        <f t="shared" si="0"/>
         <v>17186.747192074312</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -8539,11 +8541,11 @@
         <v>0.21739322173506939</v>
       </c>
       <c r="U31">
-        <f>SUM(D31:T31)</f>
+        <f t="shared" si="0"/>
         <v>20124.357080278412</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -8605,11 +8607,11 @@
         <v>0.29702706774324927</v>
       </c>
       <c r="U32">
-        <f>SUM(D32:T32)</f>
+        <f t="shared" si="0"/>
         <v>13496.520392179738</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -8671,11 +8673,11 @@
         <v>3.58613207698389</v>
       </c>
       <c r="U33">
-        <f>SUM(D33:T33)</f>
+        <f t="shared" si="0"/>
         <v>31970.765329826212</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -8737,11 +8739,11 @@
         <v>0.32624509662755891</v>
       </c>
       <c r="U34">
-        <f>SUM(D34:T34)</f>
+        <f t="shared" ref="U34:U65" si="1">SUM(D34:T34)</f>
         <v>18277.415514921711</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -8803,11 +8805,11 @@
         <v>0.40554857486587248</v>
       </c>
       <c r="U35">
-        <f>SUM(D35:T35)</f>
+        <f t="shared" si="1"/>
         <v>29402.464657113665</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -8869,11 +8871,11 @@
         <v>4.9147996613848379</v>
       </c>
       <c r="U36">
-        <f>SUM(D36:T36)</f>
+        <f t="shared" si="1"/>
         <v>53338.159748001584</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -8935,11 +8937,11 @@
         <v>0.87525151774936683</v>
       </c>
       <c r="U37">
-        <f>SUM(D37:T37)</f>
+        <f t="shared" si="1"/>
         <v>12341.029109881432</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -9001,11 +9003,11 @@
         <v>0.90893937425986804</v>
       </c>
       <c r="U38">
-        <f>SUM(D38:T38)</f>
+        <f t="shared" si="1"/>
         <v>26008.139780642527</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -9067,11 +9069,11 @@
         <v>2.9871026549350001E-4</v>
       </c>
       <c r="U39">
-        <f>SUM(D39:T39)</f>
+        <f t="shared" si="1"/>
         <v>12.241837271894765</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>70</v>
       </c>
@@ -9133,11 +9135,11 @@
         <v>9.9013092679082516E-5</v>
       </c>
       <c r="U40">
-        <f>SUM(D40:T40)</f>
+        <f t="shared" si="1"/>
         <v>10.859221303984098</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -9199,11 +9201,11 @@
         <v>3.0718601438040001E-4</v>
       </c>
       <c r="U41">
-        <f>SUM(D41:T41)</f>
+        <f t="shared" si="1"/>
         <v>0.60515901260528993</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -9265,11 +9267,11 @@
         <v>8.1717549768210002E-4</v>
       </c>
       <c r="U42">
-        <f>SUM(D42:T42)</f>
+        <f t="shared" si="1"/>
         <v>0.62292963059852147</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -9331,11 +9333,11 @@
         <v>4.1658919882816363E-5</v>
       </c>
       <c r="U43">
-        <f>SUM(D43:T43)</f>
+        <f t="shared" si="1"/>
         <v>1.6611445676325833</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>65</v>
       </c>
@@ -9397,11 +9399,11 @@
         <v>3.1425652820977619E-5</v>
       </c>
       <c r="U44">
-        <f>SUM(D44:T44)</f>
+        <f t="shared" si="1"/>
         <v>3.0654376349634669</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -9463,11 +9465,11 @@
         <v>3.0605671841635238E-5</v>
       </c>
       <c r="U45">
-        <f>SUM(D45:T45)</f>
+        <f t="shared" si="1"/>
         <v>7.8635190239668882</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -9529,11 +9531,11 @@
         <v>2.7398499721452719E-5</v>
       </c>
       <c r="U46">
-        <f>SUM(D46:T46)</f>
+        <f t="shared" si="1"/>
         <v>2.9083764442779323</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -9595,11 +9597,11 @@
         <v>1.7012523230660299E-5</v>
       </c>
       <c r="U47">
-        <f>SUM(D47:T47)</f>
+        <f t="shared" si="1"/>
         <v>0.74089305167176078</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -9661,11 +9663,11 @@
         <v>4.4734503226989188E-5</v>
       </c>
       <c r="U48">
-        <f>SUM(D48:T48)</f>
+        <f t="shared" si="1"/>
         <v>0.86564069769962837</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -9727,11 +9729,11 @@
         <v>4.2669996789178001E-3</v>
       </c>
       <c r="U49">
-        <f>SUM(D49:T49)</f>
+        <f t="shared" si="1"/>
         <v>2377.6139245204577</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -9793,11 +9795,11 @@
         <v>3.0123417411196999E-3</v>
       </c>
       <c r="U50">
-        <f>SUM(D50:T50)</f>
+        <f t="shared" si="1"/>
         <v>2367.3978229675477</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -9859,11 +9861,11 @@
         <v>2.5339858600458001E-3</v>
       </c>
       <c r="U51">
-        <f>SUM(D51:T51)</f>
+        <f t="shared" si="1"/>
         <v>40.126092851055681</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>75</v>
       </c>
@@ -9925,11 +9927,11 @@
         <v>1.4150198436243999E-3</v>
       </c>
       <c r="U52">
-        <f>SUM(D52:T52)</f>
+        <f t="shared" si="1"/>
         <v>21.148980191231139</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -9991,11 +9993,11 @@
         <v>1.7193507740167781E-5</v>
       </c>
       <c r="U53">
-        <f>SUM(D53:T53)</f>
+        <f t="shared" si="1"/>
         <v>0.74877491207658964</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -10057,11 +10059,11 @@
         <v>4.5210402374741398E-5</v>
       </c>
       <c r="U54">
-        <f>SUM(D54:T54)</f>
+        <f t="shared" si="1"/>
         <v>0.87484965594481046</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>71</v>
       </c>
@@ -10123,11 +10125,11 @@
         <v>1.7272917915617039E-6</v>
       </c>
       <c r="U55">
-        <f>SUM(D55:T55)</f>
+        <f t="shared" si="1"/>
         <v>0.36057100154568755</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -10189,11 +10191,11 @@
         <v>1.4792042859023889E-5</v>
       </c>
       <c r="U56">
-        <f>SUM(D56:T56)</f>
+        <f t="shared" si="1"/>
         <v>0.67213100839783813</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>73</v>
       </c>
@@ -10255,7 +10257,7 @@
         <v>4.3587802217343852E-5</v>
       </c>
       <c r="U57">
-        <f>SUM(D57:T57)</f>
+        <f t="shared" si="1"/>
         <v>0.61458714772303469</v>
       </c>
     </row>
@@ -10272,23 +10274,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.453125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -10326,7 +10328,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -10361,11 +10363,11 @@
         <v>2.5763906586482358E-6</v>
       </c>
       <c r="L2">
-        <f>SUM(D2:K2)</f>
+        <f t="shared" ref="L2:L33" si="0">SUM(D2:K2)</f>
         <v>1.4156177028323368E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -10400,11 +10402,11 @@
         <v>4.6651128517151124E-6</v>
       </c>
       <c r="L3">
-        <f>SUM(D3:K3)</f>
+        <f t="shared" si="0"/>
         <v>1.74116782699683E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -10439,11 +10441,11 @@
         <v>5.0565935688612607E-8</v>
       </c>
       <c r="L4">
-        <f>SUM(D4:K4)</f>
+        <f t="shared" si="0"/>
         <v>2.0257985163925616E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -10478,11 +10480,11 @@
         <v>1.530832235031708E-7</v>
       </c>
       <c r="L5">
-        <f>SUM(D5:K5)</f>
+        <f t="shared" si="0"/>
         <v>5.4095811117628327E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -10517,11 +10519,11 @@
         <v>4.9264424030097258E-8</v>
       </c>
       <c r="L6">
-        <f>SUM(D6:K6)</f>
+        <f t="shared" si="0"/>
         <v>1.9217255684051597E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -10556,11 +10558,11 @@
         <v>7.4141027648112852E-8</v>
       </c>
       <c r="L7">
-        <f>SUM(D7:K7)</f>
+        <f t="shared" si="0"/>
         <v>1.7059522102793711E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -10595,11 +10597,11 @@
         <v>2.5437215057671711E-8</v>
       </c>
       <c r="L8">
-        <f>SUM(D8:K8)</f>
+        <f t="shared" si="0"/>
         <v>9.9060727267266605E-6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -10634,11 +10636,11 @@
         <v>6.9348396917523691E-8</v>
       </c>
       <c r="L9">
-        <f>SUM(D9:K9)</f>
+        <f t="shared" si="0"/>
         <v>1.5809747817211384E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -10673,11 +10675,11 @@
         <v>5.5735173672084573E-8</v>
       </c>
       <c r="L10">
-        <f>SUM(D10:K10)</f>
+        <f t="shared" si="0"/>
         <v>4.7176474988789319E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -10712,11 +10714,11 @@
         <v>1.3301755707549371E-7</v>
       </c>
       <c r="L11">
-        <f>SUM(D11:K11)</f>
+        <f t="shared" si="0"/>
         <v>2.0261844098527509E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -10751,11 +10753,11 @@
         <v>4.8385586651313646E-9</v>
       </c>
       <c r="L12">
-        <f>SUM(D12:K12)</f>
+        <f t="shared" si="0"/>
         <v>6.8094582641600282E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -10790,11 +10792,11 @@
         <v>3.5252118413508602E-8</v>
       </c>
       <c r="L13">
-        <f>SUM(D13:K13)</f>
+        <f t="shared" si="0"/>
         <v>9.4249650494446433E-6</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -10829,11 +10831,11 @@
         <v>1.6750282027214879E-8</v>
       </c>
       <c r="L14">
-        <f>SUM(D14:K14)</f>
+        <f t="shared" si="0"/>
         <v>3.714378702381557E-6</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -10868,11 +10870,11 @@
         <v>1.4523527489821661E-7</v>
       </c>
       <c r="L15">
-        <f>SUM(D15:K15)</f>
+        <f t="shared" si="0"/>
         <v>1.3927892437360704E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -10907,11 +10909,11 @@
         <v>7.1686515666593001E-3</v>
       </c>
       <c r="L16">
-        <f>SUM(D16:K16)</f>
+        <f t="shared" si="0"/>
         <v>3.9388706606080431E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -10946,11 +10948,11 @@
         <v>1.4069665901930001E-4</v>
       </c>
       <c r="L17">
-        <f>SUM(D17:K17)</f>
+        <f t="shared" si="0"/>
         <v>5.6366618624629168E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -10985,11 +10987,11 @@
         <v>4.8313747009360003E-4</v>
       </c>
       <c r="L18">
-        <f>SUM(D18:K18)</f>
+        <f t="shared" si="0"/>
         <v>0.13275009102602789</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -11024,11 +11026,11 @@
         <v>4.3577261155389998E-4</v>
       </c>
       <c r="L19">
-        <f>SUM(D19:K19)</f>
+        <f t="shared" si="0"/>
         <v>0.18052607905591275</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -11063,11 +11065,11 @@
         <v>4.1527200650919998E-4</v>
       </c>
       <c r="L20">
-        <f>SUM(D20:K20)</f>
+        <f t="shared" si="0"/>
         <v>0.13916195800091533</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -11102,11 +11104,11 @@
         <v>2.8521279477797998E-3</v>
       </c>
       <c r="L21">
-        <f>SUM(D21:K21)</f>
+        <f t="shared" si="0"/>
         <v>0.46437611753664582</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -11141,11 +11143,11 @@
         <v>8.1637610734880005E-4</v>
       </c>
       <c r="L22">
-        <f>SUM(D22:K22)</f>
+        <f t="shared" si="0"/>
         <v>0.2225751871752584</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -11180,11 +11182,11 @@
         <v>5.2947498141070004E-4</v>
       </c>
       <c r="L23">
-        <f>SUM(D23:K23)</f>
+        <f t="shared" si="0"/>
         <v>0.24632790644070532</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -11219,11 +11221,11 @@
         <v>6.47670295047E-4</v>
       </c>
       <c r="L24">
-        <f>SUM(D24:K24)</f>
+        <f t="shared" si="0"/>
         <v>0.16166539265213153</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -11258,11 +11260,11 @@
         <v>1.5378382886113999E-3</v>
       </c>
       <c r="L25">
-        <f>SUM(D25:K25)</f>
+        <f t="shared" si="0"/>
         <v>0.38202571544552549</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -11297,11 +11299,11 @@
         <v>4.3233833726510001E-4</v>
       </c>
       <c r="L26">
-        <f>SUM(D26:K26)</f>
+        <f t="shared" si="0"/>
         <v>6.0735530848433868E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -11336,11 +11338,11 @@
         <v>1.1309207572533001E-3</v>
       </c>
       <c r="L27">
-        <f>SUM(D27:K27)</f>
+        <f t="shared" si="0"/>
         <v>0.41781989009256937</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -11375,11 +11377,11 @@
         <v>5.461855330936E-4</v>
       </c>
       <c r="L28">
-        <f>SUM(D28:K28)</f>
+        <f t="shared" si="0"/>
         <v>0.16101472371828562</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -11414,11 +11416,11 @@
         <v>3.3454665220679998E-4</v>
       </c>
       <c r="L29">
-        <f>SUM(D29:K29)</f>
+        <f t="shared" si="0"/>
         <v>0.1063544034924991</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -11453,11 +11455,11 @@
         <v>9.9846323416750006E-4</v>
       </c>
       <c r="L30">
-        <f>SUM(D30:K30)</f>
+        <f t="shared" si="0"/>
         <v>0.15209049499923247</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -11492,11 +11494,11 @@
         <v>2.898863441623E-4</v>
       </c>
       <c r="L31">
-        <f>SUM(D31:K31)</f>
+        <f t="shared" si="0"/>
         <v>0.36724683866305408</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -11531,11 +11533,11 @@
         <v>2.6461125853709998E-4</v>
       </c>
       <c r="L32">
-        <f>SUM(D32:K32)</f>
+        <f t="shared" si="0"/>
         <v>7.0746155895366092E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -11570,11 +11572,11 @@
         <v>2.7207010081971E-3</v>
       </c>
       <c r="L33">
-        <f>SUM(D33:K33)</f>
+        <f t="shared" si="0"/>
         <v>0.29638332645010468</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -11609,11 +11611,11 @@
         <v>4.1011978306590001E-4</v>
       </c>
       <c r="L34">
-        <f>SUM(D34:K34)</f>
+        <f t="shared" ref="L34:L65" si="1">SUM(D34:K34)</f>
         <v>0.21827013959679153</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -11648,11 +11650,11 @@
         <v>4.7146192077319999E-4</v>
       </c>
       <c r="L35">
-        <f>SUM(D35:K35)</f>
+        <f t="shared" si="1"/>
         <v>0.70724558169858653</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -11687,11 +11689,11 @@
         <v>4.8554597027469998E-4</v>
       </c>
       <c r="L36">
-        <f>SUM(D36:K36)</f>
+        <f t="shared" si="1"/>
         <v>0.47705373665379974</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -11726,11 +11728,11 @@
         <v>1.090172483316E-3</v>
       </c>
       <c r="L37">
-        <f>SUM(D37:K37)</f>
+        <f t="shared" si="1"/>
         <v>0.10454626208353474</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -11765,11 +11767,11 @@
         <v>6.9816581014609999E-4</v>
       </c>
       <c r="L38">
-        <f>SUM(D38:K38)</f>
+        <f t="shared" si="1"/>
         <v>0.10253651049199447</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>68</v>
       </c>
@@ -11804,11 +11806,11 @@
         <v>3.1418603125576799E-7</v>
       </c>
       <c r="L39">
-        <f>SUM(D39:K39)</f>
+        <f t="shared" si="1"/>
         <v>7.2292813064111513E-5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>70</v>
       </c>
@@ -11843,11 +11845,11 @@
         <v>1.077948050806897E-7</v>
       </c>
       <c r="L40">
-        <f>SUM(D40:K40)</f>
+        <f t="shared" si="1"/>
         <v>4.197877690191663E-5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -11882,11 +11884,11 @@
         <v>1.689381054087356E-7</v>
       </c>
       <c r="L41">
-        <f>SUM(D41:K41)</f>
+        <f t="shared" si="1"/>
         <v>4.2334357841902031E-6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>28</v>
       </c>
@@ -11921,11 +11923,11 @@
         <v>1.324311225850562E-8</v>
       </c>
       <c r="L42">
-        <f>SUM(D42:K42)</f>
+        <f t="shared" si="1"/>
         <v>8.5359831357259077E-6</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -11960,11 +11962,11 @@
         <v>4.9875502091212918E-8</v>
       </c>
       <c r="L43">
-        <f>SUM(D43:K43)</f>
+        <f t="shared" si="1"/>
         <v>1.0191631601158609E-5</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>65</v>
       </c>
@@ -11999,11 +12001,11 @@
         <v>3.9457329163446882E-8</v>
       </c>
       <c r="L44">
-        <f>SUM(D44:K44)</f>
+        <f t="shared" si="1"/>
         <v>1.0954070432990294E-5</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -12038,11 +12040,11 @@
         <v>5.2631527030061493E-8</v>
       </c>
       <c r="L45">
-        <f>SUM(D45:K45)</f>
+        <f t="shared" si="1"/>
         <v>6.426995580956293E-5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -12077,11 +12079,11 @@
         <v>3.4123004849134802E-8</v>
       </c>
       <c r="L46">
-        <f>SUM(D46:K46)</f>
+        <f t="shared" si="1"/>
         <v>1.499800464491923E-5</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -12116,11 +12118,11 @@
         <v>1.152966548262032E-6</v>
       </c>
       <c r="L47">
-        <f>SUM(D47:K47)</f>
+        <f t="shared" si="1"/>
         <v>6.3350635918550318E-6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>26</v>
       </c>
@@ -12155,11 +12157,11 @@
         <v>2.2628878892307809E-8</v>
       </c>
       <c r="L48">
-        <f>SUM(D48:K48)</f>
+        <f t="shared" si="1"/>
         <v>9.0656977978984705E-6</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -12194,11 +12196,11 @@
         <v>5.1268034162436922E-5</v>
       </c>
       <c r="L49">
-        <f>SUM(D49:K49)</f>
+        <f t="shared" si="1"/>
         <v>3.0181602980993514E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>29</v>
       </c>
@@ -12233,11 +12235,11 @@
         <v>6.2266006630937718E-6</v>
       </c>
       <c r="L50">
-        <f>SUM(D50:K50)</f>
+        <f t="shared" si="1"/>
         <v>3.7874788904981773E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -12272,11 +12274,11 @@
         <v>2.1413941533772721E-7</v>
       </c>
       <c r="L51">
-        <f>SUM(D51:K51)</f>
+        <f t="shared" si="1"/>
         <v>2.2557544112744235E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>75</v>
       </c>
@@ -12311,11 +12313,11 @@
         <v>1.1825781184550499E-7</v>
       </c>
       <c r="L52">
-        <f>SUM(D52:K52)</f>
+        <f t="shared" si="1"/>
         <v>1.9261448090097618E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -12350,11 +12352,11 @@
         <v>1.165232153160865E-6</v>
       </c>
       <c r="L53">
-        <f>SUM(D53:K53)</f>
+        <f t="shared" si="1"/>
         <v>6.4024578698531117E-6</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -12389,11 +12391,11 @@
         <v>2.2869611964525441E-8</v>
       </c>
       <c r="L54">
-        <f>SUM(D54:K54)</f>
+        <f t="shared" si="1"/>
         <v>9.1621413774803655E-6</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>71</v>
       </c>
@@ -12428,11 +12430,11 @@
         <v>1.808719549751706E-9</v>
       </c>
       <c r="L55">
-        <f>SUM(D55:K55)</f>
+        <f t="shared" si="1"/>
         <v>2.5454686564848584E-6</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -12467,11 +12469,11 @@
         <v>1.3177725097936279E-8</v>
       </c>
       <c r="L56">
-        <f>SUM(D56:K56)</f>
+        <f t="shared" si="1"/>
         <v>3.5231810243171475E-6</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>73</v>
       </c>
@@ -12506,7 +12508,7 @@
         <v>5.4290934158968303E-8</v>
       </c>
       <c r="L57">
-        <f>SUM(D57:K57)</f>
+        <f t="shared" si="1"/>
         <v>5.2064368816834837E-6</v>
       </c>
     </row>
@@ -12523,9 +12525,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:T57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12587,7 +12589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0.53659424957488422</v>
       </c>
@@ -12649,7 +12651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>0.61587606900798497</v>
       </c>
@@ -12711,7 +12713,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1493.0410351606231</v>
       </c>
@@ -12773,7 +12775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>0.24013253537503981</v>
       </c>
@@ -12835,7 +12837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.24268713954233501</v>
       </c>
@@ -12897,7 +12899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.2534112735666007</v>
       </c>
@@ -12959,7 +12961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>53.932450053311861</v>
       </c>
@@ -13021,7 +13023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.76059256914148965</v>
       </c>
@@ -13083,7 +13085,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>0.626442341201913</v>
       </c>
@@ -13145,7 +13147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2116.3028535288281</v>
       </c>
@@ -13207,7 +13209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>0.34037454087652902</v>
       </c>
@@ -13269,7 +13271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>0.34399554783756492</v>
       </c>
@@ -13331,7 +13333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>0.23384367271918671</v>
       </c>
@@ -13393,7 +13395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>41.799958320467141</v>
       </c>
@@ -13455,7 +13457,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.0822937624585709</v>
       </c>
@@ -13517,7 +13519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>0.9146466285768946</v>
       </c>
@@ -13579,7 +13581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>0.55114148062613544</v>
       </c>
@@ -13641,7 +13643,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>0.95977345560574934</v>
       </c>
@@ -13703,7 +13705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1.069681309509861</v>
       </c>
@@ -13765,7 +13767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1.1341586844676519</v>
       </c>
@@ -13827,7 +13829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>0.2146439500937912</v>
       </c>
@@ -13889,7 +13891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>0.57616081900043159</v>
       </c>
@@ -13951,7 +13953,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>0.29842283754806348</v>
       </c>
@@ -14013,7 +14015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>0.8794671237955799</v>
       </c>
@@ -14075,7 +14077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>9128.0229044833377</v>
       </c>
@@ -14137,7 +14139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>5770.0189407380603</v>
       </c>
@@ -14199,7 +14201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>8230.5845072692555</v>
       </c>
@@ -14261,7 +14263,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26213.180052341319</v>
       </c>
@@ -14323,7 +14325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>13233.610694484531</v>
       </c>
@@ -14385,7 +14387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>11594.153449687259</v>
       </c>
@@ -14447,7 +14449,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>8379.9073454637564</v>
       </c>
@@ -14509,7 +14511,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>16467.841399636411</v>
       </c>
@@ -14571,7 +14573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>4356.882221474767</v>
       </c>
@@ -14633,7 +14635,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>27794.350543666969</v>
       </c>
@@ -14695,7 +14697,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>5388.7151467323019</v>
       </c>
@@ -14757,7 +14759,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>6717.589154512717</v>
       </c>
@@ -14819,7 +14821,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>8513.2802785999811</v>
       </c>
@@ -14881,7 +14883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>4657.6612830921904</v>
       </c>
@@ -14943,7 +14945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>4324.807895437044</v>
       </c>
@@ -15005,7 +15007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>14965.14663070449</v>
       </c>
@@ -15067,7 +15069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>6951.4236837301214</v>
       </c>
@@ -15129,7 +15131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>7883.7236456400797</v>
       </c>
@@ -15191,7 +15193,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>31744.319330243052</v>
       </c>
@@ -15253,7 +15255,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>6601.501327711956</v>
       </c>
@@ -15315,7 +15317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>6693.2160446241314</v>
       </c>
@@ -15377,7 +15379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>0.58507638375666571</v>
       </c>
@@ -15439,7 +15441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>0.55249421334049975</v>
       </c>
@@ -15501,7 +15503,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1.646743258252527</v>
       </c>
@@ -15563,7 +15565,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>0.86909797129869359</v>
       </c>
@@ -15625,7 +15627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>3.875980677048231</v>
       </c>
@@ -15687,7 +15689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2.3355618347135452</v>
       </c>
@@ -15749,7 +15751,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>8.0236845823776493E-2</v>
       </c>
@@ -15811,7 +15813,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>0.21537680545680299</v>
       </c>
@@ -15873,7 +15875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>0.3287568516594247</v>
       </c>
@@ -15935,7 +15937,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>14.49076298215868</v>
       </c>
@@ -15997,7 +15999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>7.9522055614049183</v>
       </c>
@@ -16067,9 +16069,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16104,7 +16106,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>7.2316659012806106E-6</v>
       </c>
@@ -16139,7 +16141,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>8.3001447928380131E-6</v>
       </c>
@@ -16174,7 +16176,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2.0121672850087001E-2</v>
       </c>
@@ -16209,7 +16211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3.2362595559596889E-6</v>
       </c>
@@ -16244,7 +16246,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3.2706878858617221E-6</v>
       </c>
@@ -16279,7 +16281,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3.415216743686185E-6</v>
       </c>
@@ -16314,7 +16316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7.2684614176520002E-4</v>
       </c>
@@ -16349,7 +16351,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1.0250485076797289E-5</v>
       </c>
@@ -16384,7 +16386,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8.4425461535398328E-6</v>
       </c>
@@ -16419,7 +16421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2.8521355188319199E-2</v>
       </c>
@@ -16454,7 +16456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>4.5872182996932858E-6</v>
       </c>
@@ -16489,7 +16491,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>4.6360185106379994E-6</v>
       </c>
@@ -16524,7 +16526,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>3.1515047270375948E-6</v>
       </c>
@@ -16559,7 +16561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>5.6333688535920002E-4</v>
       </c>
@@ -16594,7 +16596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1.4586043184895369E-5</v>
       </c>
@@ -16629,7 +16631,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1.23266673837213E-5</v>
       </c>
@@ -16664,7 +16666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>7.4277185324402631E-6</v>
       </c>
@@ -16699,7 +16701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1.2934840388359249E-5</v>
       </c>
@@ -16734,7 +16736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1.441606550277141E-5</v>
       </c>
@@ -16769,7 +16771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1.528502530055749E-5</v>
       </c>
@@ -16804,7 +16806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2.8927505958104692E-6</v>
       </c>
@@ -16839,7 +16841,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>7.7649034637679882E-6</v>
       </c>
@@ -16874,7 +16876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>4.0218363501590797E-6</v>
       </c>
@@ -16909,7 +16911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1.185255417712127E-5</v>
       </c>
@@ -16944,7 +16946,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>0.12301811288422911</v>
       </c>
@@ -16979,7 +16981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>7.7762386108920001E-2</v>
       </c>
@@ -17014,7 +17016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>0.11092336038284541</v>
       </c>
@@ -17049,7 +17051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>0.35327430443218849</v>
       </c>
@@ -17084,7 +17086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>0.17834900625984801</v>
       </c>
@@ -17119,7 +17121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>0.15625408626245599</v>
       </c>
@@ -17154,7 +17156,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>0.11293578013549969</v>
       </c>
@@ -17189,7 +17191,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>0.2219366442680398</v>
       </c>
@@ -17224,7 +17226,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>5.8717581494351301E-2</v>
       </c>
@@ -17259,7 +17261,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>0.3745836956548142</v>
       </c>
@@ -17294,7 +17296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>7.26235653716263E-2</v>
       </c>
@@ -17329,7 +17331,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>9.0532763732496496E-2</v>
       </c>
@@ -17364,7 +17366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>0.11473324344398569</v>
       </c>
@@ -17399,7 +17401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>6.2771172643379003E-2</v>
       </c>
@@ -17434,7 +17436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>5.8285316703191203E-2</v>
       </c>
@@ -17469,7 +17471,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>0.20168486815892561</v>
       </c>
@@ -17504,7 +17506,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>9.3684145247617701E-2</v>
       </c>
@@ -17539,7 +17541,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>0.1062487261215468</v>
       </c>
@@ -17574,7 +17576,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>0.42781731612332968</v>
       </c>
@@ -17609,7 +17611,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>8.8968251364937495E-2</v>
       </c>
@@ -17644,7 +17646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>9.0204287964537111E-2</v>
       </c>
@@ -17679,7 +17681,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>7.8850582855531721E-6</v>
       </c>
@@ -17714,7 +17716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>7.4459492751624222E-6</v>
       </c>
@@ -17749,7 +17751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2.2193113472032961E-5</v>
       </c>
@@ -17784,7 +17786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1.1712809387981749E-5</v>
       </c>
@@ -17819,7 +17821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>5.2236484669541079E-5</v>
       </c>
@@ -17854,7 +17856,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>3.1476302425383667E-5</v>
       </c>
@@ -17889,7 +17891,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1.081349758338223E-6</v>
       </c>
@@ -17924,7 +17926,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2.9026272657835149E-6</v>
       </c>
@@ -17959,7 +17961,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>4.430647024730476E-6</v>
       </c>
@@ -17994,7 +17996,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1.952916130458184E-4</v>
       </c>
@@ -18029,7 +18031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1.071716550203504E-4</v>
       </c>
@@ -18071,20 +18073,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -18110,7 +18113,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -18133,7 +18136,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -18156,7 +18159,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -18179,7 +18182,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -18202,7 +18205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -18225,7 +18228,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -18248,7 +18251,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -18271,7 +18274,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -18294,7 +18297,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -18317,7 +18320,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -18340,7 +18343,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -18363,7 +18366,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -18386,7 +18389,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -18409,7 +18412,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -18432,7 +18435,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -18458,7 +18461,7 @@
         <v>0.3724666728676938</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -18484,7 +18487,7 @@
         <v>0.39771659433743412</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -18510,7 +18513,7 @@
         <v>0.22880009604623849</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -18536,7 +18539,7 @@
         <v>0.75270654536379145</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -18562,7 +18565,7 @@
         <v>0.41896461578139849</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -18588,7 +18591,7 @@
         <v>0.47839848371680987</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -18614,7 +18617,7 @@
         <v>1.4160072546741001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -18640,7 +18643,7 @@
         <v>0.20745227809544189</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -18666,7 +18669,7 @@
         <v>0.1417220000921782</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -18692,21 +18695,21 @@
         <v>1.853639984242524</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B26">
-        <v>16340.756411080971</v>
+        <v>45894.973876682721</v>
       </c>
       <c r="C26">
-        <v>2495.8322855097022</v>
+        <v>3558.5947929624972</v>
       </c>
       <c r="D26">
-        <v>96.378851515042953</v>
+        <v>159.16812374792349</v>
       </c>
       <c r="E26">
-        <v>10.79196206876032</v>
+        <v>102.32330904308721</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
@@ -18715,24 +18718,24 @@
         <v>87</v>
       </c>
       <c r="H26">
-        <v>1662.5982822965479</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9546.0308616411112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B27">
-        <v>11557.11103402108</v>
+        <v>8025.4110468692306</v>
       </c>
       <c r="C27">
-        <v>840.27182868028171</v>
+        <v>2660.1379938666878</v>
       </c>
       <c r="D27">
-        <v>43.521080744765548</v>
+        <v>149.751838681484</v>
       </c>
       <c r="E27">
-        <v>73.405464541961493</v>
+        <v>5.1102571047769576</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
@@ -18741,24 +18744,24 @@
         <v>87</v>
       </c>
       <c r="H27">
-        <v>1698.29503496041</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1376.943344466182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B28">
-        <v>15103.64335205864</v>
+        <v>20869.903368436819</v>
       </c>
       <c r="C28">
-        <v>527.73752311556359</v>
+        <v>1701.868287762891</v>
       </c>
       <c r="D28">
-        <v>27.223791623406601</v>
+        <v>108.7207527829426</v>
       </c>
       <c r="E28">
-        <v>23.39145157333212</v>
+        <v>61.163311051997191</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
@@ -18767,24 +18770,24 @@
         <v>87</v>
       </c>
       <c r="H28">
-        <v>1739.5830321281101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3276.467897931529</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>45894.973876682721</v>
+        <v>16340.756411080971</v>
       </c>
       <c r="C29">
-        <v>3558.5947929624972</v>
+        <v>2495.8322855097022</v>
       </c>
       <c r="D29">
-        <v>159.16812374792349</v>
+        <v>96.378851515042953</v>
       </c>
       <c r="E29">
-        <v>102.32330904308721</v>
+        <v>10.79196206876032</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
@@ -18793,24 +18796,24 @@
         <v>87</v>
       </c>
       <c r="H29">
-        <v>9546.0308616411112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1662.5982822965479</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B30">
-        <v>24798.813504340309</v>
+        <v>11654.736303029549</v>
       </c>
       <c r="C30">
-        <v>656.81774789536109</v>
+        <v>2368.5421512777261</v>
       </c>
       <c r="D30">
-        <v>26.390049807332311</v>
+        <v>95.122636646409603</v>
       </c>
       <c r="E30">
-        <v>38.238316413563062</v>
+        <v>17.130757508356329</v>
       </c>
       <c r="F30" t="s">
         <v>33</v>
@@ -18819,24 +18822,24 @@
         <v>87</v>
       </c>
       <c r="H30">
-        <v>3629.865692178797</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2038.712948137626</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B31">
-        <v>20869.903368436819</v>
+        <v>16912.712551519751</v>
       </c>
       <c r="C31">
-        <v>1701.868287762891</v>
+        <v>1424.2172237808529</v>
       </c>
       <c r="D31">
-        <v>108.7207527829426</v>
+        <v>92.617080523880162</v>
       </c>
       <c r="E31">
-        <v>61.163311051997191</v>
+        <v>433.00439714693943</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
@@ -18845,24 +18848,24 @@
         <v>87</v>
       </c>
       <c r="H31">
-        <v>3276.467897931529</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2737.7336450052849</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B32">
-        <v>15764.662167643841</v>
+        <v>24880.617598393979</v>
       </c>
       <c r="C32">
-        <v>1573.55140705703</v>
+        <v>1357.035665933158</v>
       </c>
       <c r="D32">
-        <v>39.392607746621429</v>
+        <v>44.794530944433681</v>
       </c>
       <c r="E32">
-        <v>34.863702214946557</v>
+        <v>90.743079860402474</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
@@ -18871,24 +18874,24 @@
         <v>87</v>
       </c>
       <c r="H32">
-        <v>2897.5634742552379</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5622.9534439671752</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B33">
-        <v>31041.327158421551</v>
+        <v>11557.11103402108</v>
       </c>
       <c r="C33">
-        <v>1488.3875491760371</v>
+        <v>840.27182868028171</v>
       </c>
       <c r="D33">
-        <v>31.51885997806356</v>
+        <v>43.521080744765548</v>
       </c>
       <c r="E33">
-        <v>116.1411215174371</v>
+        <v>73.405464541961493</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
@@ -18897,24 +18900,24 @@
         <v>87</v>
       </c>
       <c r="H33">
-        <v>5514.9756104960361</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1698.29503496041</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>8025.4110468692306</v>
+        <v>15764.662167643841</v>
       </c>
       <c r="C34">
-        <v>2660.1379938666878</v>
+        <v>1573.55140705703</v>
       </c>
       <c r="D34">
-        <v>149.751838681484</v>
+        <v>39.392607746621429</v>
       </c>
       <c r="E34">
-        <v>5.1102571047769576</v>
+        <v>34.863702214946557</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
@@ -18923,24 +18926,24 @@
         <v>87</v>
       </c>
       <c r="H34">
-        <v>1376.943344466182</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>2897.5634742552379</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>54197.026768724507</v>
+        <v>31041.327158421551</v>
       </c>
       <c r="C35">
-        <v>1250.5183072841439</v>
+        <v>1488.3875491760371</v>
       </c>
       <c r="D35">
-        <v>20.395720220676509</v>
+        <v>31.51885997806356</v>
       </c>
       <c r="E35">
-        <v>34.484274338624523</v>
+        <v>116.1411215174371</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
@@ -18949,24 +18952,24 @@
         <v>87</v>
       </c>
       <c r="H35">
-        <v>10942.78381396348</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5514.9756104960361</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B36">
-        <v>9811.0970597424912</v>
+        <v>15103.64335205864</v>
       </c>
       <c r="C36">
-        <v>331.77205714901629</v>
+        <v>527.73752311556359</v>
       </c>
       <c r="D36">
-        <v>8.0549985228643628</v>
+        <v>27.223791623406601</v>
       </c>
       <c r="E36">
-        <v>68.309142855661477</v>
+        <v>23.39145157333212</v>
       </c>
       <c r="F36" t="s">
         <v>33</v>
@@ -18975,24 +18978,24 @@
         <v>87</v>
       </c>
       <c r="H36">
-        <v>1482.65071755956</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1739.5830321281101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="B37">
-        <v>10042.79940181022</v>
+        <v>8015.4095218656639</v>
       </c>
       <c r="C37">
-        <v>1182.3014173370871</v>
+        <v>1477.598878677494</v>
       </c>
       <c r="D37">
-        <v>12.195608006262621</v>
+        <v>26.642801941770809</v>
       </c>
       <c r="E37">
-        <v>20.404062606433829</v>
+        <v>10.696981345703049</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
@@ -19001,24 +19004,24 @@
         <v>87</v>
       </c>
       <c r="H37">
-        <v>1588.44840505557</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1557.188913661895</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="B38">
-        <v>14131.153937048441</v>
+        <v>24798.813504340309</v>
       </c>
       <c r="C38">
-        <v>1898.22181845625</v>
+        <v>656.81774789536109</v>
       </c>
       <c r="D38">
-        <v>21.00066072098782</v>
+        <v>26.390049807332311</v>
       </c>
       <c r="E38">
-        <v>35.063062362219519</v>
+        <v>38.238316413563062</v>
       </c>
       <c r="F38" t="s">
         <v>33</v>
@@ -19027,24 +19030,24 @@
         <v>87</v>
       </c>
       <c r="H38">
-        <v>3590.9792952824109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3629.865692178797</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B39">
-        <v>9272.6658579429204</v>
+        <v>60454.990318625911</v>
       </c>
       <c r="C39">
-        <v>317.98374237675779</v>
+        <v>488.19685436397282</v>
       </c>
       <c r="D39">
-        <v>9.6952674702421913</v>
+        <v>24.81661445115445</v>
       </c>
       <c r="E39">
-        <v>223.4123167368835</v>
+        <v>35.045530001158859</v>
       </c>
       <c r="F39" t="s">
         <v>33</v>
@@ -19053,24 +19056,24 @@
         <v>87</v>
       </c>
       <c r="H39">
-        <v>1281.235045814484</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6728.4813012534814</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B40">
-        <v>8015.4095218656639</v>
+        <v>38966.018818344673</v>
       </c>
       <c r="C40">
-        <v>1477.598878677494</v>
+        <v>863.53304063951634</v>
       </c>
       <c r="D40">
-        <v>26.642801941770809</v>
+        <v>23.02059254932993</v>
       </c>
       <c r="E40">
-        <v>10.696981345703049</v>
+        <v>44.918089698081303</v>
       </c>
       <c r="F40" t="s">
         <v>33</v>
@@ -19079,24 +19082,24 @@
         <v>87</v>
       </c>
       <c r="H40">
-        <v>1557.188913661895</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4174.0902808890933</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B41">
-        <v>24880.617598393979</v>
+        <v>14131.153937048441</v>
       </c>
       <c r="C41">
-        <v>1357.035665933158</v>
+        <v>1898.22181845625</v>
       </c>
       <c r="D41">
-        <v>44.794530944433681</v>
+        <v>21.00066072098782</v>
       </c>
       <c r="E41">
-        <v>90.743079860402474</v>
+        <v>35.063062362219519</v>
       </c>
       <c r="F41" t="s">
         <v>33</v>
@@ -19105,24 +19108,24 @@
         <v>87</v>
       </c>
       <c r="H41">
-        <v>5622.9534439671752</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>3590.9792952824109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B42">
-        <v>12128.701026611079</v>
+        <v>54197.026768724507</v>
       </c>
       <c r="C42">
-        <v>490.33906178419602</v>
+        <v>1250.5183072841439</v>
       </c>
       <c r="D42">
-        <v>16.321971575693009</v>
+        <v>20.395720220676509</v>
       </c>
       <c r="E42">
-        <v>93.494958072628833</v>
+        <v>34.484274338624523</v>
       </c>
       <c r="F42" t="s">
         <v>33</v>
@@ -19131,24 +19134,24 @@
         <v>87</v>
       </c>
       <c r="H42">
-        <v>1749.620508096674</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>10942.78381396348</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B43">
-        <v>16912.712551519751</v>
+        <v>12128.701026611079</v>
       </c>
       <c r="C43">
-        <v>1424.2172237808529</v>
+        <v>490.33906178419602</v>
       </c>
       <c r="D43">
-        <v>92.617080523880162</v>
+        <v>16.321971575693009</v>
       </c>
       <c r="E43">
-        <v>433.00439714693943</v>
+        <v>93.494958072628833</v>
       </c>
       <c r="F43" t="s">
         <v>33</v>
@@ -19157,24 +19160,24 @@
         <v>87</v>
       </c>
       <c r="H43">
-        <v>2737.7336450052849</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1749.620508096674</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B44">
-        <v>60454.990318625911</v>
+        <v>10042.79940181022</v>
       </c>
       <c r="C44">
-        <v>488.19685436397282</v>
+        <v>1182.3014173370871</v>
       </c>
       <c r="D44">
-        <v>24.81661445115445</v>
+        <v>12.195608006262621</v>
       </c>
       <c r="E44">
-        <v>35.045530001158859</v>
+        <v>20.404062606433829</v>
       </c>
       <c r="F44" t="s">
         <v>33</v>
@@ -19183,24 +19186,24 @@
         <v>87</v>
       </c>
       <c r="H44">
-        <v>6728.4813012534814</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1588.44840505557</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="B45">
-        <v>12776.005546864641</v>
+        <v>9272.6658579429204</v>
       </c>
       <c r="C45">
-        <v>846.89548069299644</v>
+        <v>317.98374237675779</v>
       </c>
       <c r="D45">
-        <v>5.0640214771611021</v>
+        <v>9.6952674702421913</v>
       </c>
       <c r="E45">
-        <v>9.3295301237112902</v>
+        <v>223.4123167368835</v>
       </c>
       <c r="F45" t="s">
         <v>33</v>
@@ -19209,24 +19212,24 @@
         <v>87</v>
       </c>
       <c r="H45">
-        <v>13913.887681846591</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1281.235045814484</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="B46">
-        <v>38966.018818344673</v>
+        <v>9811.0970597424912</v>
       </c>
       <c r="C46">
-        <v>863.53304063951634</v>
+        <v>331.77205714901629</v>
       </c>
       <c r="D46">
-        <v>23.02059254932993</v>
+        <v>8.0549985228643628</v>
       </c>
       <c r="E46">
-        <v>44.918089698081303</v>
+        <v>68.309142855661477</v>
       </c>
       <c r="F46" t="s">
         <v>33</v>
@@ -19235,24 +19238,24 @@
         <v>87</v>
       </c>
       <c r="H46">
-        <v>4174.0902808890933</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1482.65071755956</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="B47">
-        <v>11654.736303029549</v>
+        <v>12776.005546864641</v>
       </c>
       <c r="C47">
-        <v>2368.5421512777261</v>
+        <v>846.89548069299644</v>
       </c>
       <c r="D47">
-        <v>95.122636646409603</v>
+        <v>5.0640214771611021</v>
       </c>
       <c r="E47">
-        <v>17.130757508356329</v>
+        <v>9.3295301237112902</v>
       </c>
       <c r="F47" t="s">
         <v>33</v>
@@ -19261,10 +19264,10 @@
         <v>87</v>
       </c>
       <c r="H47">
-        <v>2038.712948137626</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13913.887681846591</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -19290,7 +19293,7 @@
         <v>0.18474702014270811</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -19316,7 +19319,7 @@
         <v>0.29547866329020828</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -19342,7 +19345,7 @@
         <v>0.2246630806923102</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>67</v>
       </c>
@@ -19368,7 +19371,7 @@
         <v>0.163648356267242</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -19394,7 +19397,7 @@
         <v>1.6853961099731869</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>92</v>
       </c>
@@ -19420,7 +19423,7 @@
         <v>0.96958184759748522</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -19446,7 +19449,7 @@
         <v>5.2932291706860998E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -19472,7 +19475,7 @@
         <v>7.7548503217987605E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>95</v>
       </c>
@@ -19498,7 +19501,7 @@
         <v>0.69291600218007354</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -19524,7 +19527,7 @@
         <v>70.149123936476457</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>75</v>
       </c>
@@ -19550,7 +19553,7 @@
         <v>23.713952453561799</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>99</v>
       </c>
@@ -19576,7 +19579,7 @@
         <v>5075.7024665956014</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -19602,7 +19605,7 @@
         <v>0.38154299398669961</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>102</v>
       </c>
@@ -19628,7 +19631,7 @@
         <v>0.1934462038085133</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>103</v>
       </c>
@@ -19654,7 +19657,7 @@
         <v>43.614741136381241</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>104</v>
       </c>
@@ -19680,7 +19683,7 @@
         <v>1.239627354589055</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>105</v>
       </c>
@@ -19707,6 +19710,21 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H64" xr:uid="{00000000-0001-0000-0800-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="MetalliCan"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Copper concentrate"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:H47">
+      <sortCondition descending="1" ref="D1:D64"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19714,9 +19732,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:K130"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>145</v>
       </c>
@@ -19751,7 +19769,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -19780,7 +19798,7 @@
         <v>39.569932190889951</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -19809,7 +19827,7 @@
         <v>7.9722005310601771</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -19838,7 +19856,7 @@
         <v>1.5704599483997359</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -19867,7 +19885,7 @@
         <v>1.0705514727581349</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -19896,7 +19914,7 @@
         <v>5.9041786375509699E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -19928,7 +19946,7 @@
         <v>15.800921802494949</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -19960,7 +19978,7 @@
         <v>10.44400635499038</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -19992,7 +20010,7 @@
         <v>5.368620827337538</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -20024,7 +20042,7 @@
         <v>3.2195192150848482</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -20056,7 +20074,7 @@
         <v>1.946919350254954</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -20088,7 +20106,7 @@
         <v>0.58972012965223208</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -20120,7 +20138,7 @@
         <v>0.4916561911090927</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -20152,7 +20170,7 @@
         <v>0.34921386323675119</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -20184,7 +20202,7 @@
         <v>0.1056461142489903</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -20216,7 +20234,7 @@
         <v>0.103405789352708</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -20248,7 +20266,7 @@
         <v>5.7560241039630311E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -20280,7 +20298,7 @@
         <v>3.0532773568905179E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -20312,7 +20330,7 @@
         <v>2.7922593504146428E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -20344,7 +20362,7 @@
         <v>8.1830839784055483E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -20376,7 +20394,7 @@
         <v>6.5819072642229739E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -20408,7 +20426,7 @@
         <v>2.2043717337473269E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -20440,7 +20458,7 @@
         <v>1.1954809162242079E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -20472,7 +20490,7 @@
         <v>7.6881198384634944E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -20504,7 +20522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -20536,7 +20554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -20565,7 +20583,7 @@
         <v>36.626572060339278</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -20594,7 +20612,7 @@
         <v>1.2825618972191259</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -20623,7 +20641,7 @@
         <v>1.255066696511788</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -20652,7 +20670,7 @@
         <v>0.45342191267251308</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -20681,7 +20699,7 @@
         <v>0.14678142897327581</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -20713,7 +20731,7 @@
         <v>19.440676617624391</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -20745,7 +20763,7 @@
         <v>8.1797601356790057</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -20777,7 +20795,7 @@
         <v>6.9883054205258306</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -20809,7 +20827,7 @@
         <v>4.9902639668410789</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -20841,7 +20859,7 @@
         <v>2.2680257654638361</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -20873,7 +20891,7 @@
         <v>0.5119070650236327</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -20905,7 +20923,7 @@
         <v>0.34654949914914529</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -20937,7 +20955,7 @@
         <v>0.32742370630592338</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -20969,7 +20987,7 @@
         <v>0.26335700289779718</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -21001,7 +21019,7 @@
         <v>0.24494917207827541</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -21033,7 +21051,7 @@
         <v>0.1816174953371463</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -21065,7 +21083,7 @@
         <v>8.8255418174823005E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -21097,7 +21115,7 @@
         <v>7.7700611464883051E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -21129,7 +21147,7 @@
         <v>7.6369913064249367E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -21161,7 +21179,7 @@
         <v>6.6552781184178719E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -21193,7 +21211,7 @@
         <v>5.8458085727330467E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -21225,7 +21243,7 @@
         <v>5.6045833727643497E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -21257,7 +21275,7 @@
         <v>3.9706446477690158E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -21289,7 +21307,7 @@
         <v>3.448391157599387E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -21321,7 +21339,7 @@
         <v>2.1625202142846699E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -21353,7 +21371,7 @@
         <v>3.0209153335309029E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -21385,7 +21403,7 @@
         <v>1.919384742252729E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -21417,7 +21435,7 @@
         <v>4.1620051347445331E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -21449,7 +21467,7 @@
         <v>5.5074105868176613E-5</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -21481,7 +21499,7 @@
         <v>1.06094238904818E-5</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -21513,7 +21531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -21542,7 +21560,7 @@
         <v>39.816903123904773</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -21571,7 +21589,7 @@
         <v>9.658691137771438</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -21600,7 +21618,7 @@
         <v>1.890027365795848</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -21629,7 +21647,7 @@
         <v>1.5271926627432439</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -21658,7 +21676,7 @@
         <v>5.5990126537773501E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -21690,7 +21708,7 @@
         <v>15.61890592805613</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -21722,7 +21740,7 @@
         <v>10.44329603404911</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -21754,7 +21772,7 @@
         <v>5.8591409682485569</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -21786,7 +21804,7 @@
         <v>3.2091557610337502</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -21818,7 +21836,7 @@
         <v>3.180641943590143</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -21850,7 +21868,7 @@
         <v>0.47656825549629511</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -21882,7 +21900,7 @@
         <v>0.43264131110267517</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -21914,7 +21932,7 @@
         <v>0.1000606411031069</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -21946,7 +21964,7 @@
         <v>3.7466437735290473E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>69</v>
       </c>
@@ -21978,7 +21996,7 @@
         <v>1.557878090448837E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>69</v>
       </c>
@@ -22010,7 +22028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -22039,7 +22057,7 @@
         <v>39.622596913514492</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -22068,7 +22086,7 @@
         <v>1.271817064661533</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>28</v>
       </c>
@@ -22097,7 +22115,7 @@
         <v>1.1175367648724031</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -22126,7 +22144,7 @@
         <v>0.94784116611160807</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -22155,7 +22173,7 @@
         <v>0.15184594270222809</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -22187,7 +22205,7 @@
         <v>39.186786627583132</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>28</v>
       </c>
@@ -22219,7 +22237,7 @@
         <v>6.4364804411013941</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -22251,7 +22269,7 @@
         <v>2.5040050009101749</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>28</v>
       </c>
@@ -22283,7 +22301,7 @@
         <v>2.3427858628924989</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -22315,7 +22333,7 @@
         <v>0.98445047362664484</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -22347,7 +22365,7 @@
         <v>0.84373716855498515</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>28</v>
       </c>
@@ -22379,7 +22397,7 @@
         <v>0.56817142649647767</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -22411,7 +22429,7 @@
         <v>0.33876441322885043</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>28</v>
       </c>
@@ -22443,7 +22461,7 @@
         <v>3.7973605675340839E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>28</v>
       </c>
@@ -22475,7 +22493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -22504,7 +22522,7 @@
         <v>27.87554632321412</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -22533,7 +22551,7 @@
         <v>0.854018364677533</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>30</v>
       </c>
@@ -22562,7 +22580,7 @@
         <v>0.71452348800742671</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -22591,7 +22609,7 @@
         <v>0.19178773468696131</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -22623,7 +22641,7 @@
         <v>5.3106736297521993</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -22655,7 +22673,7 @@
         <v>0.91348783668421196</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -22687,7 +22705,7 @@
         <v>0.41099536078077042</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -22719,7 +22737,7 @@
         <v>8.6146080644910417E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -22751,7 +22769,7 @@
         <v>7.7852914751622574E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -22783,7 +22801,7 @@
         <v>2.6672557110370841E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -22815,7 +22833,7 @@
         <v>1.454871602172554E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>30</v>
       </c>
@@ -22847,7 +22865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>27</v>
       </c>
@@ -22876,7 +22894,7 @@
         <v>19.601590164234018</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>27</v>
       </c>
@@ -22905,7 +22923,7 @@
         <v>2.446315801054606</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>27</v>
       </c>
@@ -22934,7 +22952,7 @@
         <v>0.49894409390194649</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -22963,7 +22981,7 @@
         <v>0.28439929113100781</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>27</v>
       </c>
@@ -22992,7 +23010,7 @@
         <v>2.5487300038119078E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>27</v>
       </c>
@@ -23024,7 +23042,7 @@
         <v>4.5741115230647926</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>27</v>
       </c>
@@ -23056,7 +23074,7 @@
         <v>3.314338478998359</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>27</v>
       </c>
@@ -23088,7 +23106,7 @@
         <v>2.3874570016030172</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>27</v>
       </c>
@@ -23120,7 +23138,7 @@
         <v>2.1620256688214421</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>27</v>
       </c>
@@ -23152,7 +23170,7 @@
         <v>1.330488503500493</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>27</v>
       </c>
@@ -23184,7 +23202,7 @@
         <v>0.4742020686462875</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>27</v>
       </c>
@@ -23216,7 +23234,7 @@
         <v>0.46783854262483671</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>27</v>
       </c>
@@ -23248,7 +23266,7 @@
         <v>0.34051475252337648</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>27</v>
       </c>
@@ -23280,7 +23298,7 @@
         <v>0.15165887908313341</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>27</v>
       </c>
@@ -23312,7 +23330,7 @@
         <v>0.1092818210890058</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>27</v>
       </c>
@@ -23344,7 +23362,7 @@
         <v>0.1030563143173186</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>27</v>
       </c>
@@ -23376,7 +23394,7 @@
         <v>8.2891377580763662E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>27</v>
       </c>
@@ -23408,7 +23426,7 @@
         <v>2.962784104016809E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>27</v>
       </c>
@@ -23440,7 +23458,7 @@
         <v>2.7761468275861019E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>27</v>
       </c>
@@ -23472,7 +23490,7 @@
         <v>2.5177448054748901E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>27</v>
       </c>
@@ -23504,7 +23522,7 @@
         <v>1.5830905862193888E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>27</v>
       </c>
@@ -23536,7 +23554,7 @@
         <v>9.682282336009988E-4</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>27</v>
       </c>
@@ -23568,7 +23586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>27</v>
       </c>
@@ -23600,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>22</v>
       </c>
@@ -23632,7 +23650,7 @@
         <v>11.203925593477461</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>25</v>
       </c>
@@ -23664,7 +23682,7 @@
         <v>15.96813887345021</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>69</v>
       </c>
@@ -23696,7 +23714,7 @@
         <v>7.6917605486842531</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>28</v>
       </c>
@@ -23728,7 +23746,7 @@
         <v>3.645204924480391</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>30</v>
       </c>
@@ -23760,7 +23778,7 @@
         <v>63.630913714502292</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>27</v>
       </c>
@@ -23800,23 +23818,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -23854,7 +23872,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -23889,7 +23907,7 @@
         <v>63500</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -23924,7 +23942,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -23959,7 +23977,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -23994,7 +24012,7 @@
         <v>93533.694346666671</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -24029,7 +24047,7 @@
         <v>45578.436133333344</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -24067,7 +24085,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -24102,7 +24120,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -24140,7 +24158,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -24175,7 +24193,7 @@
         <v>71667.536000000007</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -24213,7 +24231,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -24248,7 +24266,7 @@
         <v>3.5165997959183581</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -24283,7 +24301,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -24318,7 +24336,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -24353,7 +24371,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -24388,7 +24406,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -24423,7 +24441,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -24458,7 +24476,7 @@
         <v>29.039084533163258</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -24493,7 +24511,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -24528,7 +24546,7 @@
         <v>1.220177609693877</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -24563,7 +24581,7 @@
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -24598,7 +24616,7 @@
         <v>2.7760508515306119</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -24633,7 +24651,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -24671,7 +24689,7 @@
         <v>130.12252666666669</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -24706,7 +24724,7 @@
         <v>4.1704080612244896</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -24744,7 +24762,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -24779,7 +24797,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -24814,7 +24832,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -24849,7 +24867,7 @@
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -24884,7 +24902,7 @@
         <v>1.2300799484693881</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>95</v>
       </c>
@@ -24922,7 +24940,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -24957,7 +24975,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -24992,7 +25010,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -25027,7 +25045,7 @@
         <v>363125</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -25062,7 +25080,7 @@
         <v>49375</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -25097,7 +25115,7 @@
         <v>84375</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -25132,7 +25150,7 @@
         <v>151450</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -25167,7 +25185,7 @@
         <v>186436.98475294121</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>92</v>
       </c>
@@ -25202,7 +25220,7 @@
         <v>343098.03921568632</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>98</v>
       </c>
@@ -25237,7 +25255,7 @@
         <v>152533.33333333331</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>94</v>
       </c>
@@ -25275,7 +25293,7 @@
         <v>23998.078283999999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -25313,7 +25331,7 @@
         <v>109797.3333333333</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -25348,7 +25366,7 @@
         <v>7204.1082352941175</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>75</v>
       </c>
